--- a/output/北塩原村_アンケート分析報告書_レビュー.xlsx
+++ b/output/北塩原村_アンケート分析報告書_レビュー.xlsx
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>第3章の該当箇所に、自己申告であり給付実績と一致しない旨を注記する。村への確認事項（当方M-13）として整理する</t>
+          <t>第3章の該当箇所に、自己申告であり給付実績と一致しない旨を注記する。村への確認事項（当方Ｍ-13）として整理する</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>行政データとして必要である旨を第6章3の留意事項に加える。当方の村への照会（M-11）と同じ事項</t>
+          <t>行政データとして必要である旨を第6章3の留意事項に加える。当方の村への照会（Ｍ-11）と同じ事項</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本レビューの過程で、当方の成果物に修正を要する点が見つかった。S-1・S-2は本日修正した。</t>
+          <t>本レビューの過程で、当方の成果物に修正を要する点が見つかった。Ｓ-1・Ｓ-2は本日修正した。</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
     <row r="5" ht="76" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>S-1</t>
+          <t>Ｓ-1</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>Ｓ-2</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>S-3</t>
+          <t>Ｓ-3</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>S-4</t>
+          <t>Ｓ-4</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>【重要】当方のＡ型の扱い（H-4・M-4）に直結する。報告書は食い違いに触れていない</t>
+          <t>【重要】当方のＡ型の扱い（H-4・Ｍ-4）に直結する。報告書は食い違いに触れていない</t>
         </is>
       </c>
     </row>
